--- a/evidence/s03a/race/s02a_finance.xlsx
+++ b/evidence/s03a/race/s02a_finance.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>b7e5bf8174faf4f1d9fd1b6f6d16f47b</t>
+    <t>8cf8d51bd9081c69803c5d00f9e8e92b</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>05260d6ef6597074376797321c425e92</t>
+    <t>8eca820f1ef0ed1e43b18f253af0a45a</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:00:52+08:00</t>
+    <t>2026-10-27T00:27:04+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/race/s02a_finance.xlsx
+++ b/evidence/s03a/race/s02a_finance.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>8cf8d51bd9081c69803c5d00f9e8e92b</t>
+    <t>2679eccd19923ab20bd3184be2e482c2</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>8eca820f1ef0ed1e43b18f253af0a45a</t>
+    <t>a1e940d271c86e4dbaa4b53d7f739c9a</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:27:04+08:00</t>
+    <t>2026-10-27T00:32:46+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/race/s02a_finance.xlsx
+++ b/evidence/s03a/race/s02a_finance.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>2679eccd19923ab20bd3184be2e482c2</t>
+    <t>c7c90a7a6a8dcdf9edf50143289e85c4</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>a1e940d271c86e4dbaa4b53d7f739c9a</t>
+    <t>6a7c697a73e9bbcbe1449a53dd5eee55</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:32:46+08:00</t>
+    <t>2026-10-27T00:40:42+08:00</t>
   </si>
   <si>
     <t>precision</t>
